--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE7A3A2B-9F21-4256-9875-8B9E07D0A2E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779390AE-D341-412C-9D45-0D4E57CF2291}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B1F51BB-9C81-4959-87B3-795EEAE10C8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2ADACA-B983-4F5F-8B27-451D6942DCB7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93DC93A3-0AEC-467C-BDA2-1EB66C263D21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9179541B-90BC-4BB5-80DA-F18898AEC082}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779390AE-D341-412C-9D45-0D4E57CF2291}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0955671-B27F-4DBB-90E7-0709B3B7595E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2ADACA-B983-4F5F-8B27-451D6942DCB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFC3AA9D-AAC6-4874-80AE-0D0587916CCF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9179541B-90BC-4BB5-80DA-F18898AEC082}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC3F4F14-4C30-4FB7-A4A1-F9C8A6F917C5}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0955671-B27F-4DBB-90E7-0709B3B7595E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47510F6B-E2D6-4771-9543-B7C3854E2BC6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFC3AA9D-AAC6-4874-80AE-0D0587916CCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E065C1B-59E6-45F0-A82D-69E35EB3B023}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC3F4F14-4C30-4FB7-A4A1-F9C8A6F917C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74EB9611-79D8-4D17-BD95-380A7892420C}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47510F6B-E2D6-4771-9543-B7C3854E2BC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAB64982-19B1-4DCC-A144-88E5D188D891}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E065C1B-59E6-45F0-A82D-69E35EB3B023}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F04F1927-8384-4193-9CD8-313A56E68509}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74EB9611-79D8-4D17-BD95-380A7892420C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67B65A2C-D968-4378-B18E-82F6FD256AB9}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAB64982-19B1-4DCC-A144-88E5D188D891}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50BD3E36-659B-4499-8304-C3258F676999}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F04F1927-8384-4193-9CD8-313A56E68509}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9B637AD-8B86-46D4-BAF5-A360EB1CDBDA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67B65A2C-D968-4378-B18E-82F6FD256AB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA2E9154-51EC-4FF8-8B6C-61F334CA5280}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50BD3E36-659B-4499-8304-C3258F676999}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92CB0723-EC96-4FAC-81EA-6E5BC835CB20}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9B637AD-8B86-46D4-BAF5-A360EB1CDBDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F355C22B-38B4-4704-BC35-4BA45DADA219}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA2E9154-51EC-4FF8-8B6C-61F334CA5280}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929EF63-2F55-440E-B473-F8B4F9F8381D}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92CB0723-EC96-4FAC-81EA-6E5BC835CB20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007D8120-B561-4DCE-8782-C4C4E63AAC3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F355C22B-38B4-4704-BC35-4BA45DADA219}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B6DB17-F17B-4946-B0E6-3E711F99E92B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929EF63-2F55-440E-B473-F8B4F9F8381D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC2297EE-AA7C-4C4D-899B-1DE91280D4CC}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1352,291 +1352,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007D8120-B561-4DCE-8782-C4C4E63AAC3D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B6DB17-F17B-4946-B0E6-3E711F99E92B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC2297EE-AA7C-4C4D-899B-1DE91280D4CC}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1352,4 +1352,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA360A7E-6A64-45C3-9F73-6CA8946D068F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6900B9A3-353A-45BF-972B-20BE71F4BBB3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8D97E0-596C-4778-87E9-2BC4BFC71BB8}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1352,291 +1352,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA360A7E-6A64-45C3-9F73-6CA8946D068F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6900B9A3-353A-45BF-972B-20BE71F4BBB3}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8D97E0-596C-4778-87E9-2BC4BFC71BB8}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1352,4 +1352,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2053A534-2975-4B9A-A428-421F728A5DD5}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D265B157-31CC-4417-BF5E-D5DC0B0FB349}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A34FBC7D-6F4C-4F7A-8940-F1A5261154A5}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2053A534-2975-4B9A-A428-421F728A5DD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E19DC35E-950D-4C82-962F-1CE15EAED0D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D265B157-31CC-4417-BF5E-D5DC0B0FB349}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B7A8634-C91C-4185-8FDB-9A0BD45E0B1C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A34FBC7D-6F4C-4F7A-8940-F1A5261154A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA70FAF0-EBBA-4194-B618-C71311803AFC}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E19DC35E-950D-4C82-962F-1CE15EAED0D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58660044-42C8-422E-BA2C-62A9F35419B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B7A8634-C91C-4185-8FDB-9A0BD45E0B1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{695E98BC-5380-4EC8-A661-7BC029DB3EE8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA70FAF0-EBBA-4194-B618-C71311803AFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6F86266-366D-4C53-9034-834A1DC1C200}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58660044-42C8-422E-BA2C-62A9F35419B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8CBC0B-185B-4410-813B-42E8CBFB5AE0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{695E98BC-5380-4EC8-A661-7BC029DB3EE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{820977DA-882F-426A-8FC9-62B8D317AADC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6F86266-366D-4C53-9034-834A1DC1C200}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0FD15F9-933B-4C20-BC25-9993821616E7}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8CBC0B-185B-4410-813B-42E8CBFB5AE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6BC56F5-1CD1-4F92-9B7A-74715E3AFDC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{820977DA-882F-426A-8FC9-62B8D317AADC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBD7AE0D-F5D9-497E-B834-539BAF08763C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0FD15F9-933B-4C20-BC25-9993821616E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A225B6B-F9EF-4E1B-BA89-F97A430DC9ED}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6BC56F5-1CD1-4F92-9B7A-74715E3AFDC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F3CA226-D0E1-42EF-81A1-E64AD74DCCB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBD7AE0D-F5D9-497E-B834-539BAF08763C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{656252EF-8A9E-4FBD-94DD-BD9359F4C8A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A225B6B-F9EF-4E1B-BA89-F97A430DC9ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFC33F60-FFAC-4C4C-ACA0-645CF00DA17D}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F3CA226-D0E1-42EF-81A1-E64AD74DCCB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6E9745E-8681-4215-A657-7B996B8F62F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{656252EF-8A9E-4FBD-94DD-BD9359F4C8A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0BD0E37-E1BB-41B5-BCCD-CF16E62324AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFC33F60-FFAC-4C4C-ACA0-645CF00DA17D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D38F91-62EE-4657-8A3F-4760ED06400A}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6E9745E-8681-4215-A657-7B996B8F62F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F0047A0-4C25-4D7E-8931-4A5DF9FBC7CB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0BD0E37-E1BB-41B5-BCCD-CF16E62324AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BBCE5C2-EEE8-4DC3-AA6B-EE1CC270AA09}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D38F91-62EE-4657-8A3F-4760ED06400A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C459DC43-7751-40E3-821E-CB26BFE4922E}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F0047A0-4C25-4D7E-8931-4A5DF9FBC7CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3473B437-1C7C-4C58-BAE1-E3837A8BDF58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BBCE5C2-EEE8-4DC3-AA6B-EE1CC270AA09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADAE2A19-2462-4463-9529-4A8B7F5AA43C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C459DC43-7751-40E3-821E-CB26BFE4922E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9675B58A-C0C8-4825-9643-D35955288891}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3473B437-1C7C-4C58-BAE1-E3837A8BDF58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531FBD77-D33B-449A-B63C-73A6573FCC67}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADAE2A19-2462-4463-9529-4A8B7F5AA43C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EA5FA2D-3C1A-4766-A320-5960D032ED9D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9675B58A-C0C8-4825-9643-D35955288891}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DE39E4B-D7E5-4ABC-AD5F-126069C5AA40}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1352,291 +1352,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531FBD77-D33B-449A-B63C-73A6573FCC67}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EA5FA2D-3C1A-4766-A320-5960D032ED9D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DE39E4B-D7E5-4ABC-AD5F-126069C5AA40}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1352,4 +1352,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E3C29BE-477F-4450-9976-96546C772117}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F36F2D3D-0366-4917-880B-9AC192E6E1D7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{406777C9-79C2-4E5C-8EAA-5F0231165A0E}"/>
 </file>